--- a/examples/06_data_cleaning/messy_data.xlsx
+++ b/examples/06_data_cleaning/messy_data.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="18">
   <si>
     <t>Seasonal rainfall in Lake Victoria and Simiyu</t>
   </si>
@@ -36,9 +36,6 @@
   </si>
   <si>
     <t>3.477mm</t>
-  </si>
-  <si>
-    <t>1.8mm</t>
   </si>
   <si>
     <t>Mar,2001-2019</t>
@@ -76,9 +73,9 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <numFmts count="1">
-    <numFmt numFmtId="1011" formatCode="0.000"/>
+    <numFmt numFmtId="171" formatCode="0.000"/>
   </numFmts>
-  <fonts count="10">
+  <fonts count="9">
     <font>
       <b val="0"/>
       <i val="0"/>
@@ -89,14 +86,14 @@
     <font>
       <b val="0"/>
       <i val="0"/>
-      <sz val="10"/>
+      <sz val="12"/>
       <color theme="1"/>
       <name val="Arial"/>
     </font>
     <font>
       <b val="0"/>
       <i val="0"/>
-      <sz val="12"/>
+      <sz val="10"/>
       <color theme="1"/>
       <name val="Arial"/>
     </font>
@@ -117,6 +114,7 @@
     <font>
       <b val="0"/>
       <i val="0"/>
+      <u/>
       <sz val="14"/>
       <color theme="1"/>
       <name val="Arial"/>
@@ -140,14 +138,6 @@
       <b/>
       <i val="0"/>
       <sz val="12"/>
-      <color theme="1"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <b val="0"/>
-      <i val="0"/>
-      <u/>
-      <sz val="14"/>
       <color theme="1"/>
       <name val="Arial"/>
     </font>
@@ -215,20 +205,6 @@
       <left style="thin">
         <color rgb="FF000000"/>
       </left>
-      <right style="thin">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF000000"/>
-      </bottom>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF000000"/>
-      </left>
       <right/>
       <top/>
       <bottom style="thin">
@@ -249,6 +225,20 @@
         <color rgb="FF000000"/>
       </right>
       <top/>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
       <bottom style="thin">
         <color rgb="FF000000"/>
       </bottom>
@@ -259,44 +249,44 @@
   </cellStyleXfs>
   <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0">
       <alignment horizontal="center" vertical="bottom" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0">
       <alignment horizontal="center" vertical="bottom" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0">
       <alignment vertical="bottom" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0">
       <alignment vertical="bottom" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0"/>
-    <xf numFmtId="1011" fontId="4" fillId="2" borderId="5" xfId="0"/>
-    <xf numFmtId="1011" fontId="1" fillId="0" borderId="5" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0"/>
+    <xf numFmtId="171" fontId="4" fillId="2" borderId="8" xfId="0"/>
+    <xf numFmtId="171" fontId="2" fillId="0" borderId="8" xfId="0">
       <alignment horizontal="right" vertical="bottom"/>
     </xf>
-    <xf numFmtId="1011" fontId="1" fillId="0" borderId="1" xfId="0">
+    <xf numFmtId="171" fontId="2" fillId="0" borderId="1" xfId="0">
       <alignment horizontal="right" vertical="bottom"/>
     </xf>
-    <xf numFmtId="1011" fontId="1" fillId="0" borderId="5" xfId="0"/>
-    <xf numFmtId="1011" fontId="1" fillId="3" borderId="5" xfId="0">
+    <xf numFmtId="171" fontId="2" fillId="0" borderId="8" xfId="0"/>
+    <xf numFmtId="171" fontId="2" fillId="3" borderId="8" xfId="0">
       <alignment horizontal="right" vertical="bottom"/>
     </xf>
-    <xf numFmtId="1011" fontId="9" fillId="0" borderId="5" xfId="0">
+    <xf numFmtId="171" fontId="5" fillId="0" borderId="8" xfId="0">
       <alignment horizontal="right" vertical="bottom"/>
     </xf>
-    <xf numFmtId="1011" fontId="6" fillId="0" borderId="5" xfId="0">
+    <xf numFmtId="171" fontId="6" fillId="0" borderId="8" xfId="0">
       <alignment horizontal="right" vertical="bottom"/>
     </xf>
-    <xf numFmtId="1011" fontId="7" fillId="0" borderId="5" xfId="0">
+    <xf numFmtId="171" fontId="7" fillId="0" borderId="8" xfId="0">
       <alignment horizontal="right" vertical="bottom"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0">
@@ -537,7 +527,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" xr:uid="{F54CAC62-91B6-43F1-0658-BA40C78C3AA8}" mc:Ignorable="x14ac xr xr2 xr3">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" xr:uid="{9D5FCB28-CA7E-AFD2-D508-457882A7AAF2}" mc:Ignorable="x14ac xr xr2 xr3">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
@@ -586,7 +576,7 @@
         <v>5</v>
       </c>
       <c r="C4" s="14">
-        <v>2.908473684</v>
+        <v>1</v>
       </c>
       <c r="D4" s="4"/>
       <c r="E4" s="4"/>
@@ -602,8 +592,8 @@
       <c r="B5" s="13" t="s">
         <v>7</v>
       </c>
-      <c r="C5" s="16" t="s">
-        <v>8</v>
+      <c r="C5" s="16">
+        <v>2</v>
       </c>
       <c r="D5" s="4"/>
       <c r="E5" s="4"/>
@@ -614,13 +604,13 @@
     </row>
     <row r="6" ht="15.75" customHeight="1">
       <c r="A6" s="12" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B6" s="17">
         <v>4.687052632</v>
       </c>
       <c r="C6" s="18">
-        <v>2.981052632</v>
+        <v>3</v>
       </c>
       <c r="D6" s="4"/>
       <c r="E6" s="4"/>
@@ -631,7 +621,7 @@
     </row>
     <row r="7" ht="15.75" customHeight="1">
       <c r="A7" s="12" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B7" s="17">
         <v>7.004526316</v>
@@ -648,7 +638,7 @@
     </row>
     <row r="8" ht="15.75" customHeight="1">
       <c r="A8" s="12" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B8" s="17">
         <v>9.362789474</v>
@@ -665,7 +655,7 @@
     </row>
     <row r="9" ht="15.75" customHeight="1">
       <c r="A9" s="12" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B9" s="14">
         <v>3.430210526</v>
@@ -682,7 +672,7 @@
     </row>
     <row r="10" ht="15.75" customHeight="1">
       <c r="A10" s="12" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B10" s="14">
         <v>1.764421053</v>
@@ -699,7 +689,7 @@
     </row>
     <row r="11" ht="15.75" customHeight="1">
       <c r="A11" s="9" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B11" s="14">
         <v>2.812631579</v>
@@ -716,7 +706,7 @@
     </row>
     <row r="12" ht="15.75" customHeight="1">
       <c r="A12" s="12" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B12" s="14">
         <v>3.978894737</v>
@@ -733,7 +723,7 @@
     </row>
     <row r="13" ht="15.75" customHeight="1">
       <c r="A13" s="12" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B13" s="17">
         <v>5.318421053</v>
@@ -750,7 +740,7 @@
     </row>
     <row r="14" ht="15.75" customHeight="1">
       <c r="A14" s="12" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B14" s="17">
         <v>5.118473684</v>
@@ -767,7 +757,7 @@
     </row>
     <row r="15" ht="15.75" customHeight="1">
       <c r="A15" s="12" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B15" s="17">
         <v>4.168105263</v>

--- a/examples/06_data_cleaning/messy_data.xlsx
+++ b/examples/06_data_cleaning/messy_data.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="19">
   <si>
     <t>Seasonal rainfall in Lake Victoria and Simiyu</t>
   </si>
@@ -36,6 +36,9 @@
   </si>
   <si>
     <t>3.477mm</t>
+  </si>
+  <si>
+    <t>1.8mm</t>
   </si>
   <si>
     <t>Mar,2001-2019</t>
@@ -73,9 +76,9 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <numFmts count="1">
-    <numFmt numFmtId="171" formatCode="0.000"/>
+    <numFmt numFmtId="1011" formatCode="0.000"/>
   </numFmts>
-  <fonts count="9">
+  <fonts count="10">
     <font>
       <b val="0"/>
       <i val="0"/>
@@ -86,25 +89,25 @@
     <font>
       <b val="0"/>
       <i val="0"/>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <b val="0"/>
+      <i val="0"/>
       <sz val="12"/>
       <color theme="1"/>
       <name val="Arial"/>
     </font>
     <font>
-      <b val="0"/>
+      <b/>
       <i val="0"/>
       <sz val="10"/>
       <color theme="1"/>
       <name val="Arial"/>
     </font>
     <font>
-      <b/>
-      <i val="0"/>
-      <sz val="10"/>
-      <color theme="1"/>
-      <name val="Arial"/>
-    </font>
-    <font>
       <b val="0"/>
       <i val="0"/>
       <sz val="10"/>
@@ -114,7 +117,6 @@
     <font>
       <b val="0"/>
       <i val="0"/>
-      <u/>
       <sz val="14"/>
       <color theme="1"/>
       <name val="Arial"/>
@@ -138,6 +140,14 @@
       <b/>
       <i val="0"/>
       <sz val="12"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <b val="0"/>
+      <i val="0"/>
+      <u/>
+      <sz val="14"/>
       <color theme="1"/>
       <name val="Arial"/>
     </font>
@@ -205,6 +215,20 @@
       <left style="thin">
         <color rgb="FF000000"/>
       </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
       <right/>
       <top/>
       <bottom style="thin">
@@ -225,20 +249,6 @@
         <color rgb="FF000000"/>
       </right>
       <top/>
-      <bottom style="thin">
-        <color rgb="FF000000"/>
-      </bottom>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF000000"/>
-      </top>
       <bottom style="thin">
         <color rgb="FF000000"/>
       </bottom>
@@ -249,44 +259,44 @@
   </cellStyleXfs>
   <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0">
       <alignment horizontal="center" vertical="bottom" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0">
       <alignment horizontal="center" vertical="bottom" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0">
       <alignment vertical="bottom" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0">
       <alignment vertical="bottom" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0"/>
-    <xf numFmtId="171" fontId="4" fillId="2" borderId="8" xfId="0"/>
-    <xf numFmtId="171" fontId="2" fillId="0" borderId="8" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0"/>
+    <xf numFmtId="1011" fontId="4" fillId="2" borderId="5" xfId="0"/>
+    <xf numFmtId="1011" fontId="1" fillId="0" borderId="5" xfId="0">
       <alignment horizontal="right" vertical="bottom"/>
     </xf>
-    <xf numFmtId="171" fontId="2" fillId="0" borderId="1" xfId="0">
+    <xf numFmtId="1011" fontId="1" fillId="0" borderId="1" xfId="0">
       <alignment horizontal="right" vertical="bottom"/>
     </xf>
-    <xf numFmtId="171" fontId="2" fillId="0" borderId="8" xfId="0"/>
-    <xf numFmtId="171" fontId="2" fillId="3" borderId="8" xfId="0">
+    <xf numFmtId="1011" fontId="1" fillId="0" borderId="5" xfId="0"/>
+    <xf numFmtId="1011" fontId="1" fillId="3" borderId="5" xfId="0">
       <alignment horizontal="right" vertical="bottom"/>
     </xf>
-    <xf numFmtId="171" fontId="5" fillId="0" borderId="8" xfId="0">
+    <xf numFmtId="1011" fontId="9" fillId="0" borderId="5" xfId="0">
       <alignment horizontal="right" vertical="bottom"/>
     </xf>
-    <xf numFmtId="171" fontId="6" fillId="0" borderId="8" xfId="0">
+    <xf numFmtId="1011" fontId="6" fillId="0" borderId="5" xfId="0">
       <alignment horizontal="right" vertical="bottom"/>
     </xf>
-    <xf numFmtId="171" fontId="7" fillId="0" borderId="8" xfId="0">
+    <xf numFmtId="1011" fontId="7" fillId="0" borderId="5" xfId="0">
       <alignment horizontal="right" vertical="bottom"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0">
@@ -527,7 +537,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" xr:uid="{9D5FCB28-CA7E-AFD2-D508-457882A7AAF2}" mc:Ignorable="x14ac xr xr2 xr3">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" xr:uid="{F54CAC62-91B6-43F1-0658-BA40C78C3AA8}" mc:Ignorable="x14ac xr xr2 xr3">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
@@ -576,7 +586,7 @@
         <v>5</v>
       </c>
       <c r="C4" s="14">
-        <v>1</v>
+        <v>2.908473684</v>
       </c>
       <c r="D4" s="4"/>
       <c r="E4" s="4"/>
@@ -592,8 +602,8 @@
       <c r="B5" s="13" t="s">
         <v>7</v>
       </c>
-      <c r="C5" s="16">
-        <v>2</v>
+      <c r="C5" s="16" t="s">
+        <v>8</v>
       </c>
       <c r="D5" s="4"/>
       <c r="E5" s="4"/>
@@ -604,13 +614,13 @@
     </row>
     <row r="6" ht="15.75" customHeight="1">
       <c r="A6" s="12" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B6" s="17">
         <v>4.687052632</v>
       </c>
       <c r="C6" s="18">
-        <v>3</v>
+        <v>2.981052632</v>
       </c>
       <c r="D6" s="4"/>
       <c r="E6" s="4"/>
@@ -621,7 +631,7 @@
     </row>
     <row r="7" ht="15.75" customHeight="1">
       <c r="A7" s="12" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B7" s="17">
         <v>7.004526316</v>
@@ -638,7 +648,7 @@
     </row>
     <row r="8" ht="15.75" customHeight="1">
       <c r="A8" s="12" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B8" s="17">
         <v>9.362789474</v>
@@ -655,7 +665,7 @@
     </row>
     <row r="9" ht="15.75" customHeight="1">
       <c r="A9" s="12" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B9" s="14">
         <v>3.430210526</v>
@@ -672,7 +682,7 @@
     </row>
     <row r="10" ht="15.75" customHeight="1">
       <c r="A10" s="12" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B10" s="14">
         <v>1.764421053</v>
@@ -689,7 +699,7 @@
     </row>
     <row r="11" ht="15.75" customHeight="1">
       <c r="A11" s="9" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B11" s="14">
         <v>2.812631579</v>
@@ -706,7 +716,7 @@
     </row>
     <row r="12" ht="15.75" customHeight="1">
       <c r="A12" s="12" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B12" s="14">
         <v>3.978894737</v>
@@ -723,7 +733,7 @@
     </row>
     <row r="13" ht="15.75" customHeight="1">
       <c r="A13" s="12" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B13" s="17">
         <v>5.318421053</v>
@@ -740,7 +750,7 @@
     </row>
     <row r="14" ht="15.75" customHeight="1">
       <c r="A14" s="12" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B14" s="17">
         <v>5.118473684</v>
@@ -757,7 +767,7 @@
     </row>
     <row r="15" ht="15.75" customHeight="1">
       <c r="A15" s="12" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B15" s="17">
         <v>4.168105263</v>
